--- a/Configs/GameConfig/Datas/course.xlsx
+++ b/Configs/GameConfig/Datas/course.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -82,6 +82,12 @@
     <t>pre_courseIds</t>
   </si>
   <si>
+    <t>need_itemIds</t>
+  </si>
+  <si>
+    <t>waste_time</t>
+  </si>
+  <si>
     <t>recommended_physique</t>
   </si>
   <si>
@@ -110,6 +116,9 @@
   </si>
   <si>
     <t>(list#sep=;),int#ref=course.TbCourse</t>
+  </si>
+  <si>
+    <t>(list#sep=;),int#ref=item.TbItem</t>
   </si>
   <si>
     <t>##group</t>
@@ -152,6 +161,12 @@
     <t>前置课程</t>
   </si>
   <si>
+    <t>需要道具</t>
+  </si>
+  <si>
+    <t>消耗时间</t>
+  </si>
+  <si>
     <t>推荐属性值</t>
   </si>
   <si>
@@ -162,6 +177,9 @@
   </si>
   <si>
     <t>文字课</t>
+  </si>
+  <si>
+    <t>体育课</t>
   </si>
 </sst>
 </file>
@@ -1115,23 +1133,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AC6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:AE7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="9.75" customWidth="1"/>
     <col min="3" max="3" width="11.625" customWidth="1"/>
     <col min="4" max="4" width="12.3833333333333" customWidth="1"/>
-    <col min="5" max="5" width="30.625" customWidth="1"/>
-    <col min="6" max="6" width="21.875" customWidth="1"/>
-    <col min="7" max="7" width="23.125" customWidth="1"/>
-    <col min="8" max="8" width="19.875" customWidth="1"/>
-    <col min="9" max="9" width="21.25" customWidth="1"/>
-    <col min="10" max="10" width="19.375" customWidth="1"/>
-    <col min="11" max="11" width="21.75" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="26.75" customWidth="1"/>
+    <col min="7" max="8" width="21.875" customWidth="1"/>
+    <col min="9" max="9" width="23.125" customWidth="1"/>
+    <col min="10" max="10" width="19.875" customWidth="1"/>
+    <col min="11" max="11" width="21.25" customWidth="1"/>
+    <col min="12" max="12" width="19.375" customWidth="1"/>
+    <col min="13" max="13" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:29">
+    <row r="1" s="1" customFormat="1" spans="1:31">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1165,8 +1184,12 @@
       <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1"/>
-      <c r="M1"/>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
       <c r="N1"/>
       <c r="O1"/>
       <c r="P1"/>
@@ -1183,8 +1206,10 @@
       <c r="AA1"/>
       <c r="AB1"/>
       <c r="AC1"/>
+      <c r="AD1"/>
+      <c r="AE1"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:29">
+    <row r="2" s="1" customFormat="1" spans="1:31">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1198,8 +1223,8 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2"/>
-      <c r="M2"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
       <c r="N2"/>
       <c r="O2"/>
       <c r="P2"/>
@@ -1216,43 +1241,49 @@
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
+      <c r="AD2"/>
+      <c r="AE2"/>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:29">
+    <row r="3" s="2" customFormat="1" spans="1:31">
       <c r="A3" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3"/>
-      <c r="M3"/>
+        <v>14</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>14</v>
+      </c>
       <c r="N3"/>
       <c r="O3"/>
       <c r="P3"/>
@@ -1269,15 +1300,17 @@
       <c r="AA3"/>
       <c r="AB3"/>
       <c r="AC3"/>
+      <c r="AD3"/>
+      <c r="AE3"/>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:29">
+    <row r="4" s="2" customFormat="1" spans="1:31">
       <c r="A4" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -1286,8 +1319,8 @@
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
-      <c r="L4"/>
-      <c r="M4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
       <c r="N4"/>
       <c r="O4"/>
       <c r="P4"/>
@@ -1304,37 +1337,43 @@
       <c r="AA4"/>
       <c r="AB4"/>
       <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:29">
+    <row r="5" s="1" customFormat="1" spans="1:31">
       <c r="A5" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="H5" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K5" s="3"/>
-      <c r="L5"/>
-      <c r="M5"/>
+      <c r="L5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" s="3"/>
       <c r="N5"/>
       <c r="O5"/>
       <c r="P5"/>
@@ -1351,13 +1390,29 @@
       <c r="AA5"/>
       <c r="AB5"/>
       <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
     </row>
-    <row r="6" spans="2:3">
+    <row r="6" spans="2:7">
       <c r="B6">
         <v>10000</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>30</v>
+      </c>
+      <c r="G6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7">
+        <v>10001</v>
+      </c>
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
